--- a/MR_UKBiobank/BinaryData/SA_Birth/MR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Birth/MR_dat.xlsx
@@ -6,18 +6,18 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="CAD" r:id="rId3" sheetId="1"/>
-    <sheet name="Fracture" r:id="rId4" sheetId="2"/>
-    <sheet name="Hypertension" r:id="rId5" sheetId="3"/>
+    <sheet name="Fracture" r:id="rId3" sheetId="1"/>
+    <sheet name="CAD" r:id="rId4" sheetId="2"/>
+    <sheet name="MI" r:id="rId5" sheetId="3"/>
     <sheet name="IS" r:id="rId6" sheetId="4"/>
-    <sheet name="MI" r:id="rId7" sheetId="5"/>
+    <sheet name="Hypertension" r:id="rId7" sheetId="5"/>
     <sheet name="T2DM" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="50">
   <si>
     <t>SNP</t>
   </si>
@@ -85,9 +85,6 @@
     <t>exposure</t>
   </si>
   <si>
-    <t>pos</t>
-  </si>
-  <si>
     <t>action</t>
   </si>
   <si>
@@ -148,25 +145,25 @@
     <t>FALSE</t>
   </si>
   <si>
+    <t>Fracture</t>
+  </si>
+  <si>
+    <t>Sclerostin</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
     <t>CAD</t>
   </si>
   <si>
-    <t>Sclerostin</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>Fracture</t>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
   <si>
     <t>Hypertension</t>
-  </si>
-  <si>
-    <t>IS</t>
-  </si>
-  <si>
-    <t>MI</t>
   </si>
   <si>
     <t>T2DM</t>
@@ -294,64 +291,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02529405969538345</v>
+        <v>0.05446618875587519</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861763531976298</v>
+        <v>0.38618231955977006</v>
       </c>
       <c r="K2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s">
         <v>42</v>
       </c>
-      <c r="L2" t="s">
+      <c r="O2" t="n">
+        <v>0.01402717502790013</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.032158802400024E-4</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>325648.0</v>
+      </c>
+      <c r="R2" t="s">
         <v>42</v>
-      </c>
-      <c r="M2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.014681899284066368</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.08492366862734163</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>325710.0</v>
-      </c>
-      <c r="R2" t="s">
-        <v>43</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -363,78 +357,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.026283757462650763</v>
+        <v>-0.05726215776995249</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28559608240459305</v>
+        <v>0.28559364712818747</v>
       </c>
       <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s">
         <v>42</v>
       </c>
-      <c r="L3" t="s">
+      <c r="O3" t="n">
+        <v>0.011672976356314325</v>
+      </c>
+      <c r="P3" t="n">
+        <v>9.31744998977341E-7</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>325648.0</v>
+      </c>
+      <c r="R3" t="s">
         <v>42</v>
-      </c>
-      <c r="M3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.012528526252695373</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.03591283588355619</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>325710.0</v>
-      </c>
-      <c r="R3" t="s">
-        <v>43</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -446,78 +437,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02137471960785234</v>
+        <v>0.0793845755854418</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41612937889533635</v>
+        <v>0.4161272294010711</v>
       </c>
       <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s">
         <v>42</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="n">
+        <v>0.01592154796470022</v>
+      </c>
+      <c r="P4" t="n">
+        <v>6.16474030027964E-7</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>325648.0</v>
+      </c>
+      <c r="R4" t="s">
         <v>42</v>
-      </c>
-      <c r="M4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.016473902544292388</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.19446273141300288</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>325710.0</v>
-      </c>
-      <c r="R4" t="s">
-        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -529,78 +517,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.036256525969759784</v>
+        <v>-0.08974742432906892</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07151914279573854</v>
+        <v>0.07151586989632978</v>
       </c>
       <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s">
         <v>42</v>
       </c>
-      <c r="L5" t="s">
+      <c r="O5" t="n">
+        <v>0.017093467311994133</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.5177489238497393E-7</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>325648.0</v>
+      </c>
+      <c r="R5" t="s">
         <v>42</v>
-      </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5" t="s">
-        <v>43</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.017486155423678505</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.038131180131115536</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>325710.0</v>
-      </c>
-      <c r="R5" t="s">
-        <v>43</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -612,78 +597,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03332481235349933</v>
+        <v>-0.05130229650856274</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25530686807282554</v>
+        <v>0.2553063430452513</v>
       </c>
       <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" t="s">
         <v>42</v>
       </c>
-      <c r="L6" t="s">
+      <c r="O6" t="n">
+        <v>0.011593277255414043</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9.636352327297116E-6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>325648.0</v>
+      </c>
+      <c r="R6" t="s">
         <v>42</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.01238624551734081</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.00713516161673343</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>325710.0</v>
-      </c>
-      <c r="R6" t="s">
-        <v>43</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -695,78 +677,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.027715522113857877</v>
+        <v>-0.09492350715161053</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840256670043905</v>
+        <v>0.07840521053407361</v>
       </c>
       <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7" t="s">
         <v>42</v>
       </c>
-      <c r="L7" t="s">
+      <c r="O7" t="n">
+        <v>0.016461533380336443</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.099086265747901E-9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>325648.0</v>
+      </c>
+      <c r="R7" t="s">
         <v>42</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
-      <c r="N7" t="s">
-        <v>43</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.01686894587374536</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.10038484611363935</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>325710.0</v>
-      </c>
-      <c r="R7" t="s">
-        <v>43</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -778,21 +757,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -883,64 +859,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05446618875587519</v>
+        <v>-0.02529405969538345</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38618231955977006</v>
+        <v>0.3861763531976298</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01402717502790013</v>
+        <v>0.014681899284066368</v>
       </c>
       <c r="P2" t="n">
-        <v>1.032158802400024E-4</v>
+        <v>0.08492366862734163</v>
       </c>
       <c r="Q2" t="n">
-        <v>325648.0</v>
+        <v>325710.0</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -952,78 +925,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05726215776995249</v>
+        <v>0.026283757462650763</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28559364712818747</v>
+        <v>0.28559608240459305</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O3" t="n">
-        <v>0.011672976356314325</v>
+        <v>0.012528526252695373</v>
       </c>
       <c r="P3" t="n">
-        <v>9.31744998977341E-7</v>
+        <v>0.03591283588355619</v>
       </c>
       <c r="Q3" t="n">
-        <v>325648.0</v>
+        <v>325710.0</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1035,78 +1005,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0793845755854418</v>
+        <v>-0.02137471960785234</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161272294010711</v>
+        <v>0.41612937889533635</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01592154796470022</v>
+        <v>0.016473902544292388</v>
       </c>
       <c r="P4" t="n">
-        <v>6.16474030027964E-7</v>
+        <v>0.19446273141300288</v>
       </c>
       <c r="Q4" t="n">
-        <v>325648.0</v>
+        <v>325710.0</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1118,78 +1085,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.08974742432906892</v>
+        <v>0.036256525969759784</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07151586989632978</v>
+        <v>0.07151914279573854</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O5" t="n">
-        <v>0.017093467311994133</v>
+        <v>0.017486155423678505</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5177489238497393E-7</v>
+        <v>0.038131180131115536</v>
       </c>
       <c r="Q5" t="n">
-        <v>325648.0</v>
+        <v>325710.0</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1201,78 +1165,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.05130229650856274</v>
+        <v>0.03332481235349933</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553063430452513</v>
+        <v>0.25530686807282554</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O6" t="n">
-        <v>0.011593277255414043</v>
+        <v>0.01238624551734081</v>
       </c>
       <c r="P6" t="n">
-        <v>9.636352327297116E-6</v>
+        <v>0.00713516161673343</v>
       </c>
       <c r="Q6" t="n">
-        <v>325648.0</v>
+        <v>325710.0</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1284,78 +1245,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.09492350715161053</v>
+        <v>0.027715522113857877</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840521053407361</v>
+        <v>0.07840256670043905</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>0.016461533380336443</v>
+        <v>0.01686894587374536</v>
       </c>
       <c r="P7" t="n">
-        <v>8.099086265747901E-9</v>
+        <v>0.10038484611363935</v>
       </c>
       <c r="Q7" t="n">
-        <v>325648.0</v>
+        <v>325710.0</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1367,21 +1325,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1472,64 +1427,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00513801660068689</v>
+        <v>-0.01727794604451405</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861889140696408</v>
+        <v>0.38618464298220284</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0067228023379815255</v>
+        <v>0.018460485271897344</v>
       </c>
       <c r="P2" t="n">
-        <v>0.44470809117663945</v>
+        <v>0.34930298023377815</v>
       </c>
       <c r="Q2" t="n">
-        <v>319468.0</v>
+        <v>325558.0</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -1541,78 +1493,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0011258129354349156</v>
+        <v>0.03308404396808673</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855872888677426</v>
+        <v>0.2855942719884014</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005686990803263278</v>
+        <v>0.015741001717552036</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8430741260099764</v>
+        <v>0.03557298962653082</v>
       </c>
       <c r="Q3" t="n">
-        <v>319468.0</v>
+        <v>325558.0</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1624,78 +1573,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.005479769427927969</v>
+        <v>-0.024370764061687335</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41612774988418244</v>
+        <v>0.4161424385209394</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007529667581937513</v>
+        <v>0.020645891525153566</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4667622585995815</v>
+        <v>0.23783435139778358</v>
       </c>
       <c r="Q4" t="n">
-        <v>319468.0</v>
+        <v>325558.0</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1707,78 +1653,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.013753209139866914</v>
+        <v>-0.0014405541548894829</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07143594976648679</v>
+        <v>0.07151567462633386</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008015314338261569</v>
+        <v>0.022211576262700188</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08618648440736683</v>
+        <v>0.9482886478015347</v>
       </c>
       <c r="Q5" t="n">
-        <v>319468.0</v>
+        <v>325558.0</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1790,78 +1733,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0018838366394349788</v>
+        <v>0.023742129733722587</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25529943531120486</v>
+        <v>0.2553093458001339</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005629979945460021</v>
+        <v>0.01554980599249952</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7379207678201551</v>
+        <v>0.1267997794151316</v>
       </c>
       <c r="Q6" t="n">
-        <v>319468.0</v>
+        <v>325558.0</v>
       </c>
       <c r="R6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1873,78 +1813,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009436626976586279</v>
+        <v>0.007085011142868088</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07831144277361113</v>
+        <v>0.07840077651294086</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007722480434781245</v>
+        <v>0.021308685404993713</v>
       </c>
       <c r="P7" t="n">
-        <v>0.22171958125750224</v>
+        <v>0.7395162306656686</v>
       </c>
       <c r="Q7" t="n">
-        <v>319468.0</v>
+        <v>325558.0</v>
       </c>
       <c r="R7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1956,21 +1893,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2061,28 +1995,25 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -2097,16 +2028,16 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>0.028975132224539953</v>
@@ -2118,7 +2049,7 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2130,42 +2061,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -2180,16 +2108,16 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
         <v>0.02448205053344941</v>
@@ -2201,7 +2129,7 @@
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2213,42 +2141,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -2263,16 +2188,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
         <v>0.032476512562888055</v>
@@ -2284,7 +2209,7 @@
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2296,42 +2221,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -2346,16 +2268,16 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
         <v>0.034530448940129806</v>
@@ -2367,7 +2289,7 @@
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2379,42 +2301,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -2429,16 +2348,16 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
         <v>0.024251088353309927</v>
@@ -2450,7 +2369,7 @@
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2462,42 +2381,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -2512,16 +2428,16 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
         <v>0.03348432846199588</v>
@@ -2533,7 +2449,7 @@
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -2545,21 +2461,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2650,64 +2563,61 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01727794604451405</v>
+        <v>0.00513801660068689</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38618464298220284</v>
+        <v>0.3861889140696408</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.018460485271897344</v>
+        <v>0.0067228023379815255</v>
       </c>
       <c r="P2" t="n">
-        <v>0.34930298023377815</v>
+        <v>0.44470809117663945</v>
       </c>
       <c r="Q2" t="n">
-        <v>325558.0</v>
+        <v>319468.0</v>
       </c>
       <c r="R2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2719,78 +2629,75 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03308404396808673</v>
+        <v>-0.0011258129354349156</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855942719884014</v>
+        <v>0.2855872888677426</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.015741001717552036</v>
+        <v>0.005686990803263278</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03557298962653082</v>
+        <v>0.8430741260099764</v>
       </c>
       <c r="Q3" t="n">
-        <v>325558.0</v>
+        <v>319468.0</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2802,78 +2709,75 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.024370764061687335</v>
+        <v>-0.005479769427927969</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161424385209394</v>
+        <v>0.41612774988418244</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.020645891525153566</v>
+        <v>0.007529667581937513</v>
       </c>
       <c r="P4" t="n">
-        <v>0.23783435139778358</v>
+        <v>0.4667622585995815</v>
       </c>
       <c r="Q4" t="n">
-        <v>325558.0</v>
+        <v>319468.0</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2885,78 +2789,75 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0014405541548894829</v>
+        <v>0.013753209139866914</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07151567462633386</v>
+        <v>0.07143594976648679</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.022211576262700188</v>
+        <v>0.008015314338261569</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9482886478015347</v>
+        <v>0.08618648440736683</v>
       </c>
       <c r="Q5" t="n">
-        <v>325558.0</v>
+        <v>319468.0</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2968,78 +2869,75 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.023742129733722587</v>
+        <v>-0.0018838366394349788</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553093458001339</v>
+        <v>0.25529943531120486</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01554980599249952</v>
+        <v>0.005629979945460021</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1267997794151316</v>
+        <v>0.7379207678201551</v>
       </c>
       <c r="Q6" t="n">
-        <v>325558.0</v>
+        <v>319468.0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3051,78 +2949,75 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007085011142868088</v>
+        <v>0.009436626976586279</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840077651294086</v>
+        <v>0.07831144277361113</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>0.021308685404993713</v>
+        <v>0.007722480434781245</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7395162306656686</v>
+        <v>0.22171958125750224</v>
       </c>
       <c r="Q7" t="n">
-        <v>325558.0</v>
+        <v>319468.0</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3134,21 +3029,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3239,28 +3131,25 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
         <v>-0.063746</v>
@@ -3275,16 +3164,16 @@
         <v>0.3863477335684914</v>
       </c>
       <c r="K2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
         <v>0.01767756174861193</v>
@@ -3296,7 +3185,7 @@
         <v>312981.0</v>
       </c>
       <c r="R2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3308,42 +3197,39 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y2" t="s">
         <v>44</v>
       </c>
-      <c r="W2" t="s">
-        <v>44</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4.1773814E7</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA2" t="e">
+      <c r="Z2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0.039983</v>
@@ -3358,16 +3244,16 @@
         <v>0.2855141366408824</v>
       </c>
       <c r="K3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
         <v>0.015036907334755144</v>
@@ -3379,7 +3265,7 @@
         <v>312981.0</v>
       </c>
       <c r="R3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -3391,42 +3277,39 @@
         <v>0.0069265306122449</v>
       </c>
       <c r="V3" t="s">
+        <v>43</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y3" t="s">
         <v>44</v>
       </c>
-      <c r="W3" t="s">
-        <v>44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.1777862E7</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA3" t="e">
+      <c r="Z3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
         <v>-0.041722</v>
@@ -3441,16 +3324,16 @@
         <v>0.41622654410331617</v>
       </c>
       <c r="K4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
         <v>0.01967321528235143</v>
@@ -3462,7 +3345,7 @@
         <v>312981.0</v>
       </c>
       <c r="R4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -3474,42 +3357,39 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" t="s">
+        <v>43</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>44</v>
       </c>
-      <c r="W4" t="s">
-        <v>44</v>
-      </c>
-      <c r="X4" t="n">
-        <v>4.1789965E7</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" t="e">
+      <c r="Z4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
         <v>0.066314</v>
@@ -3524,16 +3404,16 @@
         <v>0.07139411018560232</v>
       </c>
       <c r="K5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
         <v>0.021202947077213662</v>
@@ -3545,7 +3425,7 @@
         <v>312981.0</v>
       </c>
       <c r="R5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -3557,42 +3437,39 @@
         <v>0.0114775510204082</v>
       </c>
       <c r="V5" t="s">
+        <v>43</v>
+      </c>
+      <c r="W5" t="s">
+        <v>43</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y5" t="s">
         <v>44</v>
       </c>
-      <c r="W5" t="s">
-        <v>44</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4.1798621E7</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA5" t="e">
+      <c r="Z5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="n">
         <v>0.036955</v>
@@ -3607,16 +3484,16 @@
         <v>0.25520558755962824</v>
       </c>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>0.014877914491965133</v>
@@ -3628,7 +3505,7 @@
         <v>312981.0</v>
       </c>
       <c r="R6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3640,42 +3517,39 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
+        <v>43</v>
+      </c>
+      <c r="W6" t="s">
+        <v>43</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y6" t="s">
         <v>44</v>
       </c>
-      <c r="W6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>4.1801263E7</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA6" t="e">
+      <c r="Z6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" t="n">
         <v>0.060792</v>
@@ -3690,16 +3564,16 @@
         <v>0.07827312201060128</v>
       </c>
       <c r="K7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O7" t="n">
         <v>0.020516769712278324</v>
@@ -3711,7 +3585,7 @@
         <v>312981.0</v>
       </c>
       <c r="R7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3723,21 +3597,18 @@
         <v>0.0113857142857143</v>
       </c>
       <c r="V7" t="s">
+        <v>43</v>
+      </c>
+      <c r="W7" t="s">
+        <v>43</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="Y7" t="s">
         <v>44</v>
       </c>
-      <c r="W7" t="s">
-        <v>44</v>
-      </c>
-      <c r="X7" t="n">
-        <v>4.1808374E7</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA7" t="e">
+      <c r="Z7" t="e">
         <v>#N/A</v>
       </c>
     </row>
